--- a/datos_demo.xlsx
+++ b/datos_demo.xlsx
@@ -458,20 +458,20 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>46199</v>
+        <v>46302</v>
       </c>
       <c r="C2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D2" s="2">
         <f>C2/1.1</f>
-        <v>128.18181818181816</v>
+        <v>108.18181818181817</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -479,41 +479,41 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
-        <v>46190</v>
+        <v>46215</v>
       </c>
       <c r="C3">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D60" si="0">C3/1.1</f>
-        <v>340</v>
+        <v>168.18181818181816</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>46156</v>
+        <v>46217</v>
       </c>
       <c r="C4">
-        <v>106</v>
+        <v>341</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>96.36363636363636</v>
+        <v>310</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -521,83 +521,83 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>46046</v>
+        <v>46031</v>
       </c>
       <c r="C5">
-        <v>87</v>
+        <v>479</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>79.090909090909079</v>
+        <v>435.45454545454544</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="C6">
-        <v>328</v>
+        <v>286</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>298.18181818181813</v>
+        <v>260</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1">
-        <v>46034</v>
+        <v>46179</v>
       </c>
       <c r="C7">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>205.45454545454544</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="C8">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>377.27272727272725</v>
+        <v>359.99999999999994</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -605,23 +605,23 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>46155</v>
+        <v>46127</v>
       </c>
       <c r="C9">
-        <v>464</v>
+        <v>393</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>421.81818181818176</v>
+        <v>357.27272727272725</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -629,35 +629,35 @@
         <v>13</v>
       </c>
       <c r="B10" s="1">
-        <v>46132</v>
+        <v>46150</v>
       </c>
       <c r="C10">
-        <v>488</v>
+        <v>205</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>443.63636363636363</v>
+        <v>186.36363636363635</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>46155</v>
+        <v>46190</v>
       </c>
       <c r="C11">
-        <v>332</v>
+        <v>226</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="0"/>
-        <v>301.81818181818181</v>
+        <v>205.45454545454544</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -668,20 +668,20 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>46188</v>
+        <v>46282</v>
       </c>
       <c r="C12">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
-        <v>51.818181818181813</v>
+        <v>207.27272727272725</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -689,20 +689,20 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1">
-        <v>46047</v>
+        <v>46161</v>
       </c>
       <c r="C13">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="0"/>
-        <v>391.81818181818181</v>
+        <v>416.36363636363632</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -710,17 +710,17 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1">
-        <v>46046</v>
+        <v>46291</v>
       </c>
       <c r="C14">
-        <v>148</v>
+        <v>427</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>134.54545454545453</v>
+        <v>388.18181818181813</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -731,20 +731,20 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
-        <v>46079</v>
+        <v>46023</v>
       </c>
       <c r="C15">
-        <v>61</v>
+        <v>442</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="0"/>
-        <v>55.454545454545453</v>
+        <v>401.81818181818181</v>
       </c>
       <c r="E15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -752,62 +752,62 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1">
-        <v>46134</v>
+        <v>46080</v>
       </c>
       <c r="C16">
-        <v>435</v>
+        <v>155</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="0"/>
-        <v>395.45454545454544</v>
+        <v>140.90909090909091</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1">
-        <v>46099</v>
+        <v>46204</v>
       </c>
       <c r="C17">
-        <v>294</v>
+        <v>400</v>
       </c>
       <c r="D17" s="2">
         <f t="shared" si="0"/>
-        <v>267.27272727272725</v>
+        <v>363.63636363636363</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1">
-        <v>46143</v>
+        <v>46061</v>
       </c>
       <c r="C18">
-        <v>332</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2">
         <f t="shared" si="0"/>
-        <v>301.81818181818181</v>
+        <v>172.72727272727272</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -815,17 +815,17 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>46040</v>
+        <v>46276</v>
       </c>
       <c r="C19">
-        <v>190</v>
+        <v>430</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" si="0"/>
-        <v>172.72727272727272</v>
+        <v>390.90909090909088</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -836,83 +836,83 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>46100</v>
+        <v>46268</v>
       </c>
       <c r="C20">
-        <v>365</v>
+        <v>466</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="0"/>
-        <v>331.81818181818181</v>
+        <v>423.63636363636363</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1">
-        <v>46060</v>
+        <v>46111</v>
       </c>
       <c r="C21">
-        <v>392</v>
+        <v>287</v>
       </c>
       <c r="D21" s="2">
         <f t="shared" si="0"/>
-        <v>356.36363636363632</v>
+        <v>260.90909090909088</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B22" s="1">
-        <v>46181</v>
+        <v>46171</v>
       </c>
       <c r="C22">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="0"/>
-        <v>161.81818181818181</v>
+        <v>186.36363636363635</v>
       </c>
       <c r="E22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1">
-        <v>46128</v>
+        <v>46054</v>
       </c>
       <c r="C23">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="D23" s="2">
         <f t="shared" si="0"/>
-        <v>234.54545454545453</v>
+        <v>305.45454545454544</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -920,41 +920,41 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1">
-        <v>46156</v>
+        <v>46087</v>
       </c>
       <c r="C24">
-        <v>226</v>
+        <v>349</v>
       </c>
       <c r="D24" s="2">
         <f t="shared" si="0"/>
-        <v>205.45454545454544</v>
+        <v>317.27272727272725</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1">
-        <v>46160</v>
+        <v>46224</v>
       </c>
       <c r="C25">
-        <v>157</v>
+        <v>300</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="0"/>
-        <v>142.72727272727272</v>
+        <v>272.72727272727269</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -962,20 +962,20 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>46027</v>
+        <v>46204</v>
       </c>
       <c r="C26">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="0"/>
-        <v>293.63636363636363</v>
+        <v>296.36363636363632</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -983,41 +983,41 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1">
-        <v>46062</v>
+        <v>46087</v>
       </c>
       <c r="C27">
-        <v>189</v>
+        <v>271</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="0"/>
-        <v>171.81818181818181</v>
+        <v>246.36363636363635</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B28" s="1">
-        <v>46026</v>
+        <v>46136</v>
       </c>
       <c r="C28">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" si="0"/>
-        <v>184.54545454545453</v>
+        <v>189.99999999999997</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -1025,41 +1025,41 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B29" s="1">
-        <v>46120</v>
+        <v>46197</v>
       </c>
       <c r="C29">
-        <v>66</v>
+        <v>315</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="0"/>
-        <v>59.999999999999993</v>
+        <v>286.36363636363632</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1">
-        <v>46162</v>
+        <v>46275</v>
       </c>
       <c r="C30">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="0"/>
-        <v>376.36363636363632</v>
+        <v>309.09090909090907</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
@@ -1070,38 +1070,38 @@
         <v>27</v>
       </c>
       <c r="B31" s="1">
-        <v>46077</v>
+        <v>46177</v>
       </c>
       <c r="C31">
-        <v>175</v>
+        <v>319</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="0"/>
-        <v>159.09090909090907</v>
+        <v>290</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
-        <v>46200</v>
+        <v>46059</v>
       </c>
       <c r="C32">
-        <v>62</v>
+        <v>399</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" si="0"/>
-        <v>56.36363636363636</v>
+        <v>362.72727272727269</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -1109,20 +1109,20 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B33" s="1">
-        <v>46080</v>
+        <v>46224</v>
       </c>
       <c r="C33">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="D33" s="2">
         <f t="shared" si="0"/>
-        <v>241.81818181818178</v>
+        <v>343.63636363636363</v>
       </c>
       <c r="E33" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -1130,62 +1130,62 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B34" s="1">
-        <v>46153</v>
+        <v>46024</v>
       </c>
       <c r="C34">
-        <v>279</v>
+        <v>494</v>
       </c>
       <c r="D34" s="2">
         <f t="shared" si="0"/>
-        <v>253.63636363636363</v>
+        <v>449.09090909090907</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" s="1">
-        <v>46024</v>
+        <v>46040</v>
       </c>
       <c r="C35">
-        <v>65</v>
+        <v>227</v>
       </c>
       <c r="D35" s="2">
         <f t="shared" si="0"/>
-        <v>59.090909090909086</v>
+        <v>206.36363636363635</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B36" s="1">
-        <v>46084</v>
+        <v>46152</v>
       </c>
       <c r="C36">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2">
         <f t="shared" si="0"/>
-        <v>267.27272727272725</v>
+        <v>76.36363636363636</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -1193,41 +1193,41 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B37" s="1">
-        <v>46078</v>
+        <v>46058</v>
       </c>
       <c r="C37">
-        <v>96</v>
+        <v>426</v>
       </c>
       <c r="D37" s="2">
         <f t="shared" si="0"/>
-        <v>87.272727272727266</v>
+        <v>387.27272727272725</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" s="1">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="C38">
-        <v>122</v>
+        <v>295</v>
       </c>
       <c r="D38" s="2">
         <f t="shared" si="0"/>
-        <v>110.90909090909091</v>
+        <v>268.18181818181819</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1238,17 +1238,17 @@
         <v>14</v>
       </c>
       <c r="B39" s="1">
-        <v>46199</v>
+        <v>46126</v>
       </c>
       <c r="C39">
-        <v>464</v>
+        <v>263</v>
       </c>
       <c r="D39" s="2">
         <f t="shared" si="0"/>
-        <v>421.81818181818176</v>
+        <v>239.09090909090907</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1256,17 +1256,17 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1">
-        <v>46142</v>
+        <v>46275</v>
       </c>
       <c r="C40">
-        <v>252</v>
+        <v>374</v>
       </c>
       <c r="D40" s="2">
         <f t="shared" si="0"/>
-        <v>229.09090909090907</v>
+        <v>340</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -1277,20 +1277,20 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B41" s="1">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C41">
-        <v>314</v>
+        <v>175</v>
       </c>
       <c r="D41" s="2">
         <f t="shared" si="0"/>
-        <v>285.45454545454544</v>
+        <v>159.09090909090907</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -1298,146 +1298,146 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B42" s="1">
-        <v>46181</v>
+        <v>46283</v>
       </c>
       <c r="C42">
-        <v>327</v>
+        <v>90</v>
       </c>
       <c r="D42" s="2">
         <f t="shared" si="0"/>
-        <v>297.27272727272725</v>
+        <v>81.818181818181813</v>
       </c>
       <c r="E42" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B43" s="1">
-        <v>46150</v>
+        <v>46185</v>
       </c>
       <c r="C43">
-        <v>340</v>
+        <v>486</v>
       </c>
       <c r="D43" s="2">
         <f t="shared" si="0"/>
-        <v>309.09090909090907</v>
+        <v>441.81818181818176</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B44" s="1">
-        <v>46140</v>
+        <v>46285</v>
       </c>
       <c r="C44">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D44" s="2">
         <f t="shared" si="0"/>
-        <v>138.18181818181816</v>
+        <v>128.18181818181816</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B45" s="1">
-        <v>46163</v>
+        <v>46188</v>
       </c>
       <c r="C45">
-        <v>284</v>
+        <v>496</v>
       </c>
       <c r="D45" s="2">
         <f t="shared" si="0"/>
-        <v>258.18181818181819</v>
+        <v>450.90909090909088</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B46" s="1">
-        <v>46188</v>
+        <v>46295</v>
       </c>
       <c r="C46">
-        <v>269</v>
+        <v>453</v>
       </c>
       <c r="D46" s="2">
         <f t="shared" si="0"/>
-        <v>244.54545454545453</v>
+        <v>411.81818181818181</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B47" s="1">
-        <v>46145</v>
+        <v>46230</v>
       </c>
       <c r="C47">
-        <v>293</v>
+        <v>240</v>
       </c>
       <c r="D47" s="2">
         <f t="shared" si="0"/>
-        <v>266.36363636363632</v>
+        <v>218.18181818181816</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1">
-        <v>46133</v>
+        <v>46114</v>
       </c>
       <c r="C48">
-        <v>296</v>
+        <v>438</v>
       </c>
       <c r="D48" s="2">
         <f t="shared" si="0"/>
-        <v>269.09090909090907</v>
+        <v>398.18181818181813</v>
       </c>
       <c r="E48" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
@@ -1445,20 +1445,20 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B49" s="1">
-        <v>46202</v>
+        <v>46046</v>
       </c>
       <c r="C49">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D49" s="2">
         <f t="shared" si="0"/>
-        <v>89.090909090909079</v>
+        <v>79.090909090909079</v>
       </c>
       <c r="E49" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -1466,20 +1466,20 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B50" s="1">
-        <v>46142</v>
+        <v>46242</v>
       </c>
       <c r="C50">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="D50" s="2">
         <f t="shared" si="0"/>
-        <v>176.36363636363635</v>
+        <v>142.72727272727272</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -1487,41 +1487,41 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B51" s="1">
-        <v>46208</v>
+        <v>46086</v>
       </c>
       <c r="C51">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="D51" s="2">
         <f t="shared" si="0"/>
-        <v>306.36363636363632</v>
+        <v>223.63636363636363</v>
       </c>
       <c r="E51" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B52" s="1">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C52">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="D52" s="2">
         <f t="shared" si="0"/>
-        <v>179.09090909090907</v>
+        <v>74.545454545454533</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
@@ -1529,104 +1529,104 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B53" s="1">
-        <v>46070</v>
+        <v>46113</v>
       </c>
       <c r="C53">
-        <v>135</v>
+        <v>451</v>
       </c>
       <c r="D53" s="2">
         <f t="shared" si="0"/>
-        <v>122.72727272727272</v>
+        <v>409.99999999999994</v>
       </c>
       <c r="E53" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B54" s="1">
-        <v>46092</v>
+        <v>46114</v>
       </c>
       <c r="C54">
-        <v>458</v>
+        <v>71</v>
       </c>
       <c r="D54" s="2">
         <f t="shared" si="0"/>
-        <v>416.36363636363632</v>
+        <v>64.545454545454547</v>
       </c>
       <c r="E54" t="s">
         <v>5</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B55" s="1">
-        <v>46209</v>
+        <v>46245</v>
       </c>
       <c r="C55">
-        <v>179</v>
+        <v>357</v>
       </c>
       <c r="D55" s="2">
         <f t="shared" si="0"/>
-        <v>162.72727272727272</v>
+        <v>324.5454545454545</v>
       </c>
       <c r="E55" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B56" s="1">
-        <v>46144</v>
+        <v>46234</v>
       </c>
       <c r="C56">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="D56" s="2">
         <f t="shared" si="0"/>
-        <v>83.636363636363626</v>
+        <v>166.36363636363635</v>
       </c>
       <c r="E56" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B57" s="1">
-        <v>46026</v>
+        <v>46309</v>
       </c>
       <c r="C57">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="D57" s="2">
         <f t="shared" si="0"/>
-        <v>393.63636363636363</v>
+        <v>70.909090909090907</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" t="s">
         <v>10</v>
@@ -1634,20 +1634,20 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B58" s="1">
-        <v>46113</v>
+        <v>46130</v>
       </c>
       <c r="C58">
-        <v>200</v>
+        <v>398</v>
       </c>
       <c r="D58" s="2">
         <f t="shared" si="0"/>
-        <v>181.81818181818181</v>
+        <v>361.81818181818181</v>
       </c>
       <c r="E58" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
         <v>10</v>
@@ -1655,20 +1655,20 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B59" s="1">
-        <v>46073</v>
+        <v>46309</v>
       </c>
       <c r="C59">
-        <v>342</v>
+        <v>488</v>
       </c>
       <c r="D59" s="2">
         <f t="shared" si="0"/>
-        <v>310.90909090909088</v>
+        <v>443.63636363636363</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
         <v>10</v>
@@ -1676,23 +1676,23 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B60" s="1">
-        <v>46069</v>
+        <v>46117</v>
       </c>
       <c r="C60">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="D60" s="2">
         <f t="shared" si="0"/>
-        <v>117.27272727272727</v>
+        <v>153.63636363636363</v>
       </c>
       <c r="E60" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">

--- a/datos_demo.xlsx
+++ b/datos_demo.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="19">
   <si>
     <t>fecha</t>
   </si>
@@ -140,13 +140,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -428,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12" customWidth="1"/>
@@ -458,20 +460,20 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1">
-        <v>46302</v>
+        <v>46091</v>
       </c>
       <c r="C2">
-        <v>119</v>
+        <v>271</v>
       </c>
       <c r="D2" s="2">
         <f>C2/1.1</f>
-        <v>108.18181818181817</v>
+        <v>246.36363636363635</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -479,17 +481,17 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>46215</v>
+        <v>46153</v>
       </c>
       <c r="C3">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D60" si="0">C3/1.1</f>
-        <v>168.18181818181816</v>
+        <f t="shared" ref="D3:D66" si="0">C3/1.1</f>
+        <v>157.27272727272725</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -500,41 +502,41 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>46217</v>
+        <v>46081</v>
       </c>
       <c r="C4">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>310</v>
+        <v>244.54545454545453</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="C5">
-        <v>479</v>
+        <v>122</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>435.45454545454544</v>
+        <v>110.90909090909091</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -542,38 +544,38 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="C6">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>260</v>
+        <v>308.18181818181813</v>
       </c>
       <c r="E6" t="s">
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
-        <v>46179</v>
+        <v>46199</v>
       </c>
       <c r="C7">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>160</v>
+        <v>238.18181818181816</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
@@ -584,41 +586,41 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1">
-        <v>46169</v>
+        <v>46222</v>
       </c>
       <c r="C8">
-        <v>396</v>
+        <v>480</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>359.99999999999994</v>
+        <v>436.36363636363632</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>46127</v>
+        <v>46188</v>
       </c>
       <c r="C9">
-        <v>393</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>357.27272727272725</v>
+        <v>225.45454545454544</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -626,62 +628,62 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1">
-        <v>46150</v>
+        <v>46044</v>
       </c>
       <c r="C10">
-        <v>205</v>
+        <v>487</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>186.36363636363635</v>
+        <v>442.72727272727269</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C11">
-        <v>226</v>
+        <v>479</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="0"/>
-        <v>205.45454545454544</v>
+        <v>435.45454545454544</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="C12">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
-        <v>207.27272727272725</v>
+        <v>217.27272727272725</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -689,20 +691,20 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>46161</v>
+        <v>46082</v>
       </c>
       <c r="C13">
-        <v>458</v>
+        <v>96</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="0"/>
-        <v>416.36363636363632</v>
+        <v>87.272727272727266</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -710,20 +712,20 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1">
-        <v>46291</v>
+        <v>46065</v>
       </c>
       <c r="C14">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>388.18181818181813</v>
+        <v>72.72727272727272</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -731,17 +733,17 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>46023</v>
+        <v>46266</v>
       </c>
       <c r="C15">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="0"/>
-        <v>401.81818181818181</v>
+        <v>452.72727272727269</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -752,20 +754,20 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1">
-        <v>46080</v>
+        <v>46264</v>
       </c>
       <c r="C16">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="0"/>
-        <v>140.90909090909091</v>
+        <v>125.45454545454544</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>10</v>
@@ -773,41 +775,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>46204</v>
+        <v>46138</v>
       </c>
       <c r="C17">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="D17" s="2">
         <f t="shared" si="0"/>
-        <v>363.63636363636363</v>
+        <v>340.90909090909088</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>46061</v>
+        <v>46160</v>
       </c>
       <c r="C18">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D18" s="2">
         <f t="shared" si="0"/>
-        <v>172.72727272727272</v>
+        <v>158.18181818181816</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -815,20 +817,20 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1">
-        <v>46276</v>
+        <v>46071</v>
       </c>
       <c r="C19">
-        <v>430</v>
+        <v>285</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" si="0"/>
-        <v>390.90909090909088</v>
+        <v>259.09090909090907</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -836,41 +838,41 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1">
-        <v>46268</v>
+        <v>46309</v>
       </c>
       <c r="C20">
-        <v>466</v>
+        <v>362</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="0"/>
-        <v>423.63636363636363</v>
+        <v>329.09090909090907</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1">
-        <v>46111</v>
+        <v>46048</v>
       </c>
       <c r="C21">
-        <v>287</v>
+        <v>125</v>
       </c>
       <c r="D21" s="2">
         <f t="shared" si="0"/>
-        <v>260.90909090909088</v>
+        <v>113.63636363636363</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>10</v>
@@ -878,23 +880,23 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B22" s="1">
-        <v>46171</v>
+        <v>46246</v>
       </c>
       <c r="C22">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="0"/>
-        <v>186.36363636363635</v>
+        <v>164.54545454545453</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -902,59 +904,59 @@
         <v>16</v>
       </c>
       <c r="B23" s="1">
-        <v>46054</v>
+        <v>46204</v>
       </c>
       <c r="C23">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="D23" s="2">
         <f t="shared" si="0"/>
-        <v>305.45454545454544</v>
+        <v>282.72727272727269</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1">
-        <v>46087</v>
+        <v>46122</v>
       </c>
       <c r="C24">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D24" s="2">
         <f t="shared" si="0"/>
-        <v>317.27272727272725</v>
+        <v>300</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1">
-        <v>46224</v>
+        <v>46283</v>
       </c>
       <c r="C25">
-        <v>300</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="0"/>
-        <v>272.72727272727269</v>
+        <v>158.18181818181816</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -962,65 +964,65 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>46204</v>
+        <v>46295</v>
       </c>
       <c r="C26">
-        <v>326</v>
+        <v>440</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="0"/>
-        <v>296.36363636363632</v>
+        <v>399.99999999999994</v>
       </c>
       <c r="E26" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1">
-        <v>46087</v>
+        <v>46052</v>
       </c>
       <c r="C27">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="0"/>
-        <v>246.36363636363635</v>
+        <v>180.90909090909091</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B28" s="1">
-        <v>46136</v>
+        <v>46168</v>
       </c>
       <c r="C28">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" si="0"/>
-        <v>189.99999999999997</v>
+        <v>110.90909090909091</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,17 +1030,17 @@
         <v>14</v>
       </c>
       <c r="B29" s="1">
-        <v>46197</v>
+        <v>46166</v>
       </c>
       <c r="C29">
-        <v>315</v>
+        <v>220</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="0"/>
-        <v>286.36363636363632</v>
+        <v>199.99999999999997</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -1046,104 +1048,104 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B30" s="1">
-        <v>46275</v>
+        <v>46306</v>
       </c>
       <c r="C30">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="0"/>
-        <v>309.09090909090907</v>
+        <v>344.5454545454545</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="1">
-        <v>46177</v>
+        <v>46257</v>
       </c>
       <c r="C31">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="0"/>
-        <v>290</v>
+        <v>292.72727272727269</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B32" s="1">
-        <v>46059</v>
+        <v>46230</v>
       </c>
       <c r="C32">
-        <v>399</v>
+        <v>500</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" si="0"/>
-        <v>362.72727272727269</v>
+        <v>454.5454545454545</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="1">
-        <v>46224</v>
+        <v>46167</v>
       </c>
       <c r="C33">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="D33" s="2">
         <f t="shared" si="0"/>
-        <v>343.63636363636363</v>
+        <v>388.18181818181813</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1">
-        <v>46024</v>
+        <v>46166</v>
       </c>
       <c r="C34">
-        <v>494</v>
+        <v>239</v>
       </c>
       <c r="D34" s="2">
         <f t="shared" si="0"/>
-        <v>449.09090909090907</v>
+        <v>217.27272727272725</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -1151,44 +1153,44 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B35" s="1">
-        <v>46040</v>
+        <v>46061</v>
       </c>
       <c r="C35">
-        <v>227</v>
+        <v>487</v>
       </c>
       <c r="D35" s="2">
         <f t="shared" si="0"/>
-        <v>206.36363636363635</v>
+        <v>442.72727272727269</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B36" s="1">
-        <v>46152</v>
+        <v>46133</v>
       </c>
       <c r="C36">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D36" s="2">
         <f t="shared" si="0"/>
-        <v>76.36363636363636</v>
+        <v>79.090909090909079</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1196,17 +1198,17 @@
         <v>30</v>
       </c>
       <c r="B37" s="1">
-        <v>46058</v>
+        <v>46091</v>
       </c>
       <c r="C37">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="D37" s="2">
         <f t="shared" si="0"/>
-        <v>387.27272727272725</v>
+        <v>409.99999999999994</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -1214,20 +1216,20 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B38" s="1">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="C38">
-        <v>295</v>
+        <v>380</v>
       </c>
       <c r="D38" s="2">
         <f t="shared" si="0"/>
-        <v>268.18181818181819</v>
+        <v>345.45454545454544</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1235,20 +1237,20 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B39" s="1">
-        <v>46126</v>
+        <v>46066</v>
       </c>
       <c r="C39">
-        <v>263</v>
+        <v>104</v>
       </c>
       <c r="D39" s="2">
         <f t="shared" si="0"/>
-        <v>239.09090909090907</v>
+        <v>94.545454545454533</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1256,20 +1258,20 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B40" s="1">
-        <v>46275</v>
+        <v>46178</v>
       </c>
       <c r="C40">
-        <v>374</v>
+        <v>439</v>
       </c>
       <c r="D40" s="2">
         <f t="shared" si="0"/>
-        <v>340</v>
+        <v>399.09090909090907</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
@@ -1277,17 +1279,17 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B41" s="1">
-        <v>46262</v>
+        <v>46047</v>
       </c>
       <c r="C41">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2">
         <f t="shared" si="0"/>
-        <v>159.09090909090907</v>
+        <v>73.636363636363626</v>
       </c>
       <c r="E41" t="s">
         <v>4</v>
@@ -1298,41 +1300,41 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B42" s="1">
-        <v>46283</v>
+        <v>46135</v>
       </c>
       <c r="C42">
-        <v>90</v>
+        <v>463</v>
       </c>
       <c r="D42" s="2">
         <f t="shared" si="0"/>
-        <v>81.818181818181813</v>
+        <v>420.90909090909088</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B43" s="1">
-        <v>46185</v>
+        <v>46043</v>
       </c>
       <c r="C43">
-        <v>486</v>
+        <v>53</v>
       </c>
       <c r="D43" s="2">
         <f t="shared" si="0"/>
-        <v>441.81818181818176</v>
+        <v>48.18181818181818</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -1340,17 +1342,17 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B44" s="1">
-        <v>46285</v>
+        <v>46095</v>
       </c>
       <c r="C44">
-        <v>141</v>
+        <v>417</v>
       </c>
       <c r="D44" s="2">
         <f t="shared" si="0"/>
-        <v>128.18181818181816</v>
+        <v>379.09090909090907</v>
       </c>
       <c r="E44" t="s">
         <v>4</v>
@@ -1361,38 +1363,38 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B45" s="1">
-        <v>46188</v>
+        <v>46049</v>
       </c>
       <c r="C45">
-        <v>496</v>
+        <v>285</v>
       </c>
       <c r="D45" s="2">
         <f t="shared" si="0"/>
-        <v>450.90909090909088</v>
+        <v>259.09090909090907</v>
       </c>
       <c r="E45" t="s">
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B46" s="1">
-        <v>46295</v>
+        <v>46168</v>
       </c>
       <c r="C46">
-        <v>453</v>
+        <v>135</v>
       </c>
       <c r="D46" s="2">
         <f t="shared" si="0"/>
-        <v>411.81818181818181</v>
+        <v>122.72727272727272</v>
       </c>
       <c r="E46" t="s">
         <v>4</v>
@@ -1403,20 +1405,20 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B47" s="1">
-        <v>46230</v>
+        <v>46063</v>
       </c>
       <c r="C47">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="D47" s="2">
         <f t="shared" si="0"/>
-        <v>218.18181818181816</v>
+        <v>173.63636363636363</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -1424,59 +1426,59 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B48" s="1">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C48">
-        <v>438</v>
+        <v>79</v>
       </c>
       <c r="D48" s="2">
         <f t="shared" si="0"/>
-        <v>398.18181818181813</v>
+        <v>71.818181818181813</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B49" s="1">
-        <v>46046</v>
+        <v>46169</v>
       </c>
       <c r="C49">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="D49" s="2">
         <f t="shared" si="0"/>
-        <v>79.090909090909079</v>
+        <v>199.09090909090907</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1">
-        <v>46242</v>
+        <v>46142</v>
       </c>
       <c r="C50">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="D50" s="2">
         <f t="shared" si="0"/>
-        <v>142.72727272727272</v>
+        <v>84.545454545454533</v>
       </c>
       <c r="E50" t="s">
         <v>5</v>
@@ -1487,23 +1489,23 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B51" s="1">
-        <v>46086</v>
+        <v>46188</v>
       </c>
       <c r="C51">
-        <v>246</v>
+        <v>117</v>
       </c>
       <c r="D51" s="2">
         <f t="shared" si="0"/>
-        <v>223.63636363636363</v>
+        <v>106.36363636363636</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,80 +1513,80 @@
         <v>10</v>
       </c>
       <c r="B52" s="1">
-        <v>46122</v>
+        <v>46024</v>
       </c>
       <c r="C52">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="D52" s="2">
         <f t="shared" si="0"/>
-        <v>74.545454545454533</v>
+        <v>233.63636363636363</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" s="1">
-        <v>46113</v>
+        <v>46182</v>
       </c>
       <c r="C53">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D53" s="2">
         <f t="shared" si="0"/>
-        <v>409.99999999999994</v>
+        <v>419.99999999999994</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B54" s="1">
-        <v>46114</v>
+        <v>46182</v>
       </c>
       <c r="C54">
-        <v>71</v>
+        <v>222</v>
       </c>
       <c r="D54" s="2">
         <f t="shared" si="0"/>
-        <v>64.545454545454547</v>
+        <v>201.81818181818181</v>
       </c>
       <c r="E54" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55" s="1">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="C55">
-        <v>357</v>
+        <v>170</v>
       </c>
       <c r="D55" s="2">
         <f t="shared" si="0"/>
-        <v>324.5454545454545</v>
+        <v>154.54545454545453</v>
       </c>
       <c r="E55" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F55" t="s">
         <v>10</v>
@@ -1592,38 +1594,38 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B56" s="1">
-        <v>46234</v>
+        <v>46273</v>
       </c>
       <c r="C56">
-        <v>183</v>
+        <v>397</v>
       </c>
       <c r="D56" s="2">
         <f t="shared" si="0"/>
-        <v>166.36363636363635</v>
+        <v>360.90909090909088</v>
       </c>
       <c r="E56" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B57" s="1">
-        <v>46309</v>
+        <v>46283</v>
       </c>
       <c r="C57">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="D57" s="2">
         <f t="shared" si="0"/>
-        <v>70.909090909090907</v>
+        <v>286.36363636363632</v>
       </c>
       <c r="E57" t="s">
         <v>4</v>
@@ -1634,41 +1636,41 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B58" s="1">
-        <v>46130</v>
+        <v>46195</v>
       </c>
       <c r="C58">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="D58" s="2">
         <f t="shared" si="0"/>
-        <v>361.81818181818181</v>
+        <v>386.36363636363632</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B59" s="1">
-        <v>46309</v>
+        <v>46235</v>
       </c>
       <c r="C59">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="D59" s="2">
         <f t="shared" si="0"/>
-        <v>443.63636363636363</v>
+        <v>433.63636363636363</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F59" t="s">
         <v>10</v>
@@ -1679,29 +1681,861 @@
         <v>10</v>
       </c>
       <c r="B60" s="1">
-        <v>46117</v>
+        <v>46158</v>
       </c>
       <c r="C60">
-        <v>169</v>
+        <v>490</v>
       </c>
       <c r="D60" s="2">
         <f t="shared" si="0"/>
-        <v>153.63636363636363</v>
+        <v>445.45454545454544</v>
       </c>
       <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>10</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C61" s="7">
+        <v>50</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="0"/>
+        <v>45.454545454545453</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>22</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46302</v>
+      </c>
+      <c r="C62" s="6">
+        <v>349</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="0"/>
+        <v>317.27272727272725</v>
+      </c>
+      <c r="E62" t="s">
         <v>4</v>
       </c>
-      <c r="F60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>10</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C63" s="6">
+        <v>421</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="0"/>
+        <v>382.72727272727269</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C64">
+        <v>390</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="0"/>
+        <v>354.5454545454545</v>
+      </c>
+      <c r="E64" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>16</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C65">
+        <v>154</v>
+      </c>
+      <c r="D65" s="2">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="E65" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>20</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C66">
+        <v>367</v>
+      </c>
+      <c r="D66" s="2">
+        <f t="shared" si="0"/>
+        <v>333.63636363636363</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>29</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46216</v>
+      </c>
+      <c r="C67">
+        <v>469</v>
+      </c>
+      <c r="D67" s="2">
+        <f t="shared" ref="D67:D100" si="1">C67/1.1</f>
+        <v>426.36363636363632</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>19</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46259</v>
+      </c>
+      <c r="C68">
+        <v>184</v>
+      </c>
+      <c r="D68" s="2">
+        <f t="shared" si="1"/>
+        <v>167.27272727272725</v>
+      </c>
+      <c r="E68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>20</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46045</v>
+      </c>
+      <c r="C69">
+        <v>375</v>
+      </c>
+      <c r="D69" s="2">
+        <f t="shared" si="1"/>
+        <v>340.90909090909088</v>
+      </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>27</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46024</v>
+      </c>
+      <c r="C70">
+        <v>247</v>
+      </c>
+      <c r="D70" s="2">
+        <f t="shared" si="1"/>
+        <v>224.54545454545453</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>23</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46144</v>
+      </c>
+      <c r="C71">
+        <v>381</v>
+      </c>
+      <c r="D71" s="2">
+        <f t="shared" si="1"/>
+        <v>346.36363636363632</v>
+      </c>
+      <c r="E71" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>24</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C72">
+        <v>348</v>
+      </c>
+      <c r="D72" s="2">
+        <f t="shared" si="1"/>
+        <v>316.36363636363632</v>
+      </c>
+      <c r="E72" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>20</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C73">
+        <v>149</v>
+      </c>
+      <c r="D73" s="2">
+        <f t="shared" si="1"/>
+        <v>135.45454545454544</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>20</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46211</v>
+      </c>
+      <c r="C74">
+        <v>61</v>
+      </c>
+      <c r="D74" s="2">
+        <f t="shared" si="1"/>
+        <v>55.454545454545453</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>21</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C75">
+        <v>142</v>
+      </c>
+      <c r="D75" s="2">
+        <f t="shared" si="1"/>
+        <v>129.09090909090909</v>
+      </c>
+      <c r="E75" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>29</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46309</v>
+      </c>
+      <c r="C76">
+        <v>253</v>
+      </c>
+      <c r="D76" s="2">
+        <f t="shared" si="1"/>
+        <v>229.99999999999997</v>
+      </c>
+      <c r="E76" t="s">
+        <v>6</v>
+      </c>
+      <c r="F76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>10</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C77">
+        <v>293</v>
+      </c>
+      <c r="D77" s="2">
+        <f t="shared" si="1"/>
+        <v>266.36363636363632</v>
+      </c>
+      <c r="E77" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>13</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46163</v>
+      </c>
+      <c r="C78">
+        <v>297</v>
+      </c>
+      <c r="D78" s="2">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="E78" t="s">
+        <v>7</v>
+      </c>
+      <c r="F78" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>23</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46303</v>
+      </c>
+      <c r="C79">
+        <v>373</v>
+      </c>
+      <c r="D79" s="2">
+        <f t="shared" si="1"/>
+        <v>339.09090909090907</v>
+      </c>
+      <c r="E79" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>22</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46299</v>
+      </c>
+      <c r="C80">
+        <v>56</v>
+      </c>
+      <c r="D80" s="2">
+        <f t="shared" si="1"/>
+        <v>50.909090909090907</v>
+      </c>
+      <c r="E80" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>30</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46120</v>
+      </c>
+      <c r="C81">
+        <v>81</v>
+      </c>
+      <c r="D81" s="2">
+        <f t="shared" si="1"/>
+        <v>73.636363636363626</v>
+      </c>
+      <c r="E81" t="s">
+        <v>7</v>
+      </c>
+      <c r="F81" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>24</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C82">
+        <v>356</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" si="1"/>
+        <v>323.63636363636363</v>
+      </c>
+      <c r="E82" t="s">
+        <v>4</v>
+      </c>
+      <c r="F82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>26</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46182</v>
+      </c>
+      <c r="C83">
+        <v>454</v>
+      </c>
+      <c r="D83" s="2">
+        <f t="shared" si="1"/>
+        <v>412.72727272727269</v>
+      </c>
+      <c r="E83" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>14</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46246</v>
+      </c>
+      <c r="C84">
+        <v>453</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" si="1"/>
+        <v>411.81818181818181</v>
+      </c>
+      <c r="E84" t="s">
+        <v>7</v>
+      </c>
+      <c r="F84" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>30</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C85">
+        <v>416</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="1"/>
+        <v>378.18181818181813</v>
+      </c>
+      <c r="E85" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>16</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46307</v>
+      </c>
+      <c r="C86">
+        <v>77</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="E86" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>24</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46295</v>
+      </c>
+      <c r="C87">
+        <v>500</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="1"/>
+        <v>454.5454545454545</v>
+      </c>
+      <c r="E87" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>12</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46294</v>
+      </c>
+      <c r="C88">
+        <v>274</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" si="1"/>
+        <v>249.09090909090907</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>29</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46104</v>
+      </c>
+      <c r="C89">
+        <v>275</v>
+      </c>
+      <c r="D89" s="2">
+        <f t="shared" si="1"/>
+        <v>249.99999999999997</v>
+      </c>
+      <c r="E89" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>24</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C90">
+        <v>491</v>
+      </c>
+      <c r="D90" s="2">
+        <f t="shared" si="1"/>
+        <v>446.36363636363632</v>
+      </c>
+      <c r="E90" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>17</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46037</v>
+      </c>
+      <c r="C91">
+        <v>303</v>
+      </c>
+      <c r="D91" s="2">
+        <f t="shared" si="1"/>
+        <v>275.45454545454544</v>
+      </c>
+      <c r="E91" t="s">
+        <v>7</v>
+      </c>
+      <c r="F91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>14</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C92">
+        <v>136</v>
+      </c>
+      <c r="D92" s="2">
+        <f t="shared" si="1"/>
+        <v>123.63636363636363</v>
+      </c>
+      <c r="E92" t="s">
+        <v>6</v>
+      </c>
+      <c r="F92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>25</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C93">
+        <v>212</v>
+      </c>
+      <c r="D93" s="2">
+        <f t="shared" si="1"/>
+        <v>192.72727272727272</v>
+      </c>
+      <c r="E93" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>14</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46134</v>
+      </c>
+      <c r="C94">
+        <v>350</v>
+      </c>
+      <c r="D94" s="2">
+        <f t="shared" si="1"/>
+        <v>318.18181818181813</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>21</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C95">
+        <v>322</v>
+      </c>
+      <c r="D95" s="2">
+        <f t="shared" si="1"/>
+        <v>292.72727272727269</v>
+      </c>
+      <c r="E95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>30</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46060</v>
+      </c>
+      <c r="C96">
+        <v>54</v>
+      </c>
+      <c r="D96" s="2">
+        <f t="shared" si="1"/>
+        <v>49.090909090909086</v>
+      </c>
+      <c r="E96" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>25</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46275</v>
+      </c>
+      <c r="C97">
+        <v>298</v>
+      </c>
+      <c r="D97" s="2">
+        <f t="shared" si="1"/>
+        <v>270.90909090909088</v>
+      </c>
+      <c r="E97" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>25</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46272</v>
+      </c>
+      <c r="C98">
+        <v>231</v>
+      </c>
+      <c r="D98" s="2">
+        <f t="shared" si="1"/>
+        <v>209.99999999999997</v>
+      </c>
+      <c r="E98" t="s">
+        <v>5</v>
+      </c>
+      <c r="F98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>14</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C99">
+        <v>265</v>
+      </c>
+      <c r="D99" s="2">
+        <f t="shared" si="1"/>
+        <v>240.90909090909088</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>27</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46257</v>
+      </c>
+      <c r="C100">
+        <v>206</v>
+      </c>
+      <c r="D100" s="2">
+        <f t="shared" si="1"/>
+        <v>187.27272727272725</v>
+      </c>
+      <c r="E100" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
